--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,31 +152,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,19 +805,19 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="N4" s="11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P4" s="11" t="n">
+      <c r="N4" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="11" t="n">
@@ -836,22 +827,26 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>45.2</v>
+        <v>4.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="W4" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W4" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>7.6</v>
+      </c>
       <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -866,46 +861,44 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>26.8</v>
+      <c r="F5" s="11" t="n">
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>17.6</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="N5" s="11" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P5" s="11" t="n">
+      <c r="N5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="11" t="n">
@@ -918,22 +911,22 @@
         <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>10.2</v>
+        <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="15" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="W5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="W5" s="11" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>16.2</v>
+        <v>76.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -955,10 +948,10 @@
       <c r="D6" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="E6" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -971,25 +964,23 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
+        <v>921.2</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>20</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="P6" s="11" t="n">
-        <v>-0.1</v>
       </c>
       <c r="Q6" s="11" t="n">
         <v>29.5</v>
@@ -1001,25 +992,25 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>20.6</v>
+        <v>390.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>21.3</v>
+      <c r="W6" s="11" t="n">
+        <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>17.8</v>
+        <v>27.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>4</v>
+        <v>24.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1047,8 +1038,8 @@
       <c r="G7" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="12" t="n">
-        <v>79.8</v>
+      <c r="H7" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1057,22 +1048,22 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L7" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>-0.1</v>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q7" s="11" t="n">
         <v>20.1</v>
@@ -1092,17 +1083,17 @@
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="11" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>86.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1117,9 +1108,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="11" t="n">
         <v>26.8</v>
       </c>
@@ -1136,7 +1125,7 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.2</v>
@@ -1144,19 +1133,17 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="N8" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P8" s="11" t="n">
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="n">
+        <v>791.2</v>
+      </c>
+      <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="11" t="n">
@@ -1169,25 +1156,25 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>6.6</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W8" s="3" t="n">
+      <c r="V8" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W8" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>69.2</v>
+        <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.3</v>
+        <v>27.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,53 +1190,53 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="D9" s="9" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>54.8</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>944.1</v>
-      </c>
-      <c r="L9" s="16" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="M9" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="L9" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
+      <c r="M9" s="9" t="n">
+        <v>3972.6</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>100.1</v>
+        <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>452.5</v>
+        <v>451.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="16" t="n">
+      <c r="Q9" s="9" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="16" t="n">
-        <v>110.9</v>
+      <c r="R9" s="9" t="n">
+        <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122</v>
+        <v>122.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
@@ -1257,19 +1244,21 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="16" t="n">
+      <c r="V9" s="9" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="W9" s="9" t="n">
         <v>11</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1283,77 +1272,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>91.59999999999999</v>
+        <v>23.7</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>11.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L10" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="M10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="N10" s="11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>0</v>
+      <c r="N10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q10" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="9" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="16" t="n">
+      <c r="V10" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="11" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.2</v>
+        <v>62.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1370,10 +1357,10 @@
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="11" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>23.8</v>
@@ -1381,51 +1368,47 @@
       <c r="G11" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>18.3</v>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>91.59999999999999</v>
+      </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="15" t="n">
-        <v>2.3</v>
+      <c r="R11" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>26.8</v>
@@ -1433,7 +1416,9 @@
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
       </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1447,9 +1432,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="11" t="n">
         <v>26.5</v>
       </c>
@@ -1459,38 +1442,38 @@
       <c r="F12" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>89.40000000000001</v>
+      <c r="G12" s="10" t="n">
+        <v>98.40000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>8.6</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>1.9</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22.6</v>
+        <v>2.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>24.2</v>
+        <v>8.4</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1499,25 +1482,25 @@
         <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="11" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>24.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>83.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.5</v>
+        <v>82.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1537,13 +1520,13 @@
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.9</v>
+        <v>89.3</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1552,22 +1535,22 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="12" t="n">
-        <v>19.2</v>
+      <c r="L13" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.3</v>
+        <v>0.4</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
@@ -1585,7 +1568,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>31.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1597,10 +1580,10 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>85.2</v>
+        <v>12</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1615,7 +1598,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D14" s="11" t="n">
         <v>29.9</v>
       </c>
@@ -1629,24 +1614,26 @@
         <v>19.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
       </c>
@@ -1660,16 +1647,16 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.6</v>
+        <v>25.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>88.2</v>
+        <v>58.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="12" t="n">
-        <v>15.1</v>
+      <c r="V14" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="W14" s="11" t="n">
         <v>22.8</v>
@@ -1678,7 +1665,7 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>717.2</v>
+        <v>27.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>51.4</v>
@@ -1696,32 +1683,30 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="11" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
@@ -1730,22 +1715,22 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.5</v>
+        <v>91.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q15" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="12" t="n">
-        <v>22.7</v>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1754,7 +1739,7 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="W15" s="11" t="n">
         <v>20.9</v>
@@ -1766,7 +1751,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,71 +1767,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="16" t="n">
-        <v>1940.4</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>114.6</v>
+      <c r="D16" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>48.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L16" s="16" t="n">
-        <v>951.3</v>
-      </c>
-      <c r="M16" s="16" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="9" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="M16" s="9" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>853.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q16" s="16" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="R16" s="16" t="n">
-        <v>1127.3</v>
+        <v>1.4</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>122.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>18.2</v>
+        <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="V16" s="16" t="n">
-        <v>984.8</v>
-      </c>
-      <c r="W16" s="16" t="n">
-        <v>1124.6</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>99.2</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>124.6</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>10064.6</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr"/>
+        <v>970.8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1861,17 +1848,17 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="16" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>23.3</v>
+      <c r="D17" s="9" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1880,39 +1867,41 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4.8</v>
+        <v>22.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="16" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+      <c r="M17" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>9.1</v>
+        <v>21.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="16" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="R17" s="16" t="n">
+      <c r="Q17" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R17" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="12" t="n">
-        <v>35.3</v>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V17" s="16" t="n">
-        <v>22.7</v>
+        <v>82.2</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>22.9</v>
       </c>
       <c r="W17" s="11" t="n">
         <v>21.5</v>
@@ -1921,9 +1910,11 @@
         <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1942,41 +1933,43 @@
         <v>30.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="15" t="n">
+      <c r="M18" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>91.2</v>
+        <v>291.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>29.2</v>
+      <c r="Q18" s="10" t="n">
+        <v>89.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1985,10 +1978,10 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
+        <v>1</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
@@ -1997,12 +1990,14 @@
         <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>24.3</v>
+        <v>25.3</v>
       </c>
       <c r="Y18" s="3" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="Z18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2017,25 +2012,25 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="G19" s="11" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46.9</v>
+        <v>15.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>2.5</v>
@@ -2043,19 +2038,19 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="O19" s="11" t="n">
-        <v>99</v>
-      </c>
-      <c r="P19" s="11" t="n">
+      <c r="M19" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
@@ -2071,21 +2066,23 @@
         <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>19.9</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2099,18 +2096,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>9.6</v>
+      <c r="C20" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>59.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2122,51 +2121,51 @@
         <v>2.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M20" s="11" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="11" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="15" t="n">
+      <c r="L20" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>72.2</v>
+        <v>22.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="15" t="n">
-        <v>81.8</v>
+      <c r="V20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="3" t="n">
-        <v>22.1</v>
+      <c r="X20" s="8" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2180,21 +2179,23 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>21.2</v>
+      <c r="C21" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>23.4</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2203,9 +2204,9 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="L21" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2219,31 +2220,35 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="R21" s="15" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>1.3</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.3</v>
+        <v>88.7</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="W21" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2257,15 +2262,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>32.8</v>
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>23.6</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
@@ -2277,54 +2284,56 @@
         <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="N22" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="11" t="n">
+      <c r="N22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>991.2</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="R22" s="15" t="n">
-        <v>2.3</v>
+      <c r="Q22" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8956.200000000001</v>
+        <v>86.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>24.6</v>
+      <c r="V22" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="W22" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X22" s="3" t="n">
+      <c r="Y22" s="3" t="n">
         <v>80.2</v>
       </c>
-      <c r="Y22" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2339,71 +2348,73 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="16" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="9" t="n">
+        <v>1942.6</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="F23" s="16" t="n">
-        <v>119.2</v>
+      <c r="F23" s="9" t="n">
+        <v>112.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.2</v>
+        <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.8</v>
+        <v>23.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L23" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L23" s="9" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="M23" s="16" t="n">
-        <v>92.90000000000001</v>
+      <c r="M23" s="9" t="n">
+        <v>1952.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>43.1</v>
+        <v>951.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="16" t="n">
+      <c r="Q23" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="16" t="n">
-        <v>107.9</v>
+      <c r="R23" s="9" t="n">
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="V23" s="16" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="W23" s="16" t="n">
-        <v>19.7</v>
+        <v>37.7</v>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94927.8</v>
+        <v>198.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>9425.6</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2417,7 +2428,9 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D24" s="11" t="n">
         <v>28.5</v>
       </c>
@@ -2434,51 +2447,57 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="16" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="M24" s="16" t="n">
+      <c r="L24" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="M24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>581.2</v>
+        <v>91.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q24" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q24" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="S24" s="12" t="n">
-        <v>823.9</v>
+      <c r="R24" s="9" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>78.2</v>
+        <v>72.3</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="16" t="n">
+      <c r="V24" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="X24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="n">
+        <v>23.5</v>
+      </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2492,70 +2511,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>1.8</v>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="11" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>18.8</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="G25" s="10" t="n">
+        <v>44.4</v>
+      </c>
       <c r="H25" s="3" t="n">
-        <v>1.7</v>
+        <v>17.9</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.4</v>
+        <v>34.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="15" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="M25" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>12.9</v>
+      </c>
       <c r="N25" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>24.2</v>
+        <v>59.2</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V25" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X25" s="12" t="n">
-        <v>71.3</v>
+      <c r="W25" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>69.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2571,18 +2592,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>111.6</v>
+      </c>
       <c r="D26" s="11" t="n">
-        <v>28.6</v>
+        <v>32.6</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>1.6</v>
@@ -2594,17 +2617,19 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>19.6</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>98.96000000000001</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2613,10 +2638,10 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2624,11 +2649,11 @@
       <c r="U26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>21.3</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>86.2</v>
@@ -2636,7 +2661,9 @@
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="n">
+        <v>24.5</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2661,40 +2688,40 @@
         <v>22.4</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.9</v>
+        <v>19.8</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>11.8</v>
+      <c r="M27" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.4</v>
+        <v>922.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="15" t="n">
-        <v>2.6</v>
+      <c r="Q27" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2703,19 +2730,23 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W27" s="13" t="inlineStr"/>
       <c r="X27" s="3" t="n">
-        <v>80.2</v>
+        <v>24</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>80.2</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2731,16 +2762,16 @@
       </c>
       <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="11" t="n">
-        <v>32.7</v>
+        <v>30.7</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>16.8</v>
+      <c r="G28" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2752,51 +2783,53 @@
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>16.2</v>
+        <v>0.3</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.1</v>
+        <v>14.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1272.4</v>
+        <v>92.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R28" s="15" t="n">
-        <v>2.3</v>
+        <v>20.9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.6</v>
+        <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>40.2</v>
+        <v>4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W28" s="12" t="n">
-        <v>22.8</v>
+      <c r="V28" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="W28" s="10" t="n">
+        <v>2.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.4</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>53.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2812,25 +2845,25 @@
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="11" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>11.7</v>
+      <c r="G29" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
@@ -2838,15 +2871,17 @@
       <c r="L29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M29" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="M29" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>40.7</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2855,16 +2890,16 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>20.1</v>
+        <v>12.9</v>
+      </c>
+      <c r="V29" s="11" t="n">
+        <v>13.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2875,7 +2910,9 @@
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2890,17 +2927,17 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="16" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>119.1</v>
+      <c r="D30" s="9" t="n">
+        <v>1498.4</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>11.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>5.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
@@ -2909,29 +2946,29 @@
         <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K30" s="16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L30" s="16" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="M30" s="16" t="n">
-        <v>96.09999999999999</v>
+        <v>17.8</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>392.1</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="16" t="n">
+      <c r="Q30" s="9" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="16" t="n">
-        <v>112.7</v>
+      <c r="R30" s="9" t="n">
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
@@ -2942,19 +2979,21 @@
       <c r="U30" s="3" t="n">
         <v>118.2</v>
       </c>
-      <c r="V30" s="16" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W30" s="16" t="n">
-        <v>117.6</v>
+      <c r="V30" s="9" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="W30" s="9" t="n">
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>374.2</v>
+        <v>312.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>52.4</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2970,35 +3009,35 @@
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="11" t="n">
-        <v>35.9</v>
+        <v>29.9</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.9</v>
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="16" t="n">
+      <c r="L31" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="M31" s="16" t="n">
+      <c r="M31" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.5</v>
+        <v>28.4</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3006,34 +3045,36 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="16" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="R31" s="16" t="n">
-        <v>82.8</v>
+      <c r="Q31" s="9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="R31" s="9" t="n">
+        <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="16" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W31" s="16" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>77.3</v>
+      <c r="V31" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W31" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>23.6</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3047,70 +3088,76 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>25.6</v>
+      <c r="C32" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>35</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>29.1</v>
+        <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>9.6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q32" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="11" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="S32" s="11" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="T32" s="11" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="U32" s="11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>22.2</v>
+      <c r="S32" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V32" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="W32" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>85.3</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3124,14 +3171,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="15" t="n">
-        <v>4.2</v>
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="15" t="n">
+      <c r="F33" s="10" t="n">
         <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3149,36 +3198,36 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>18.8</v>
+      <c r="M33" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="11" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="S33" s="11" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="T33" s="11" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="U33" s="11" t="n">
-        <v>2.5</v>
+      <c r="R33" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="W33" s="11" t="n">
         <v>27.4</v>
@@ -3189,7 +3238,9 @@
       <c r="Y33" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3205,10 +3256,10 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="11" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>25.8</v>
@@ -3216,7 +3267,7 @@
       <c r="G34" s="11" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3226,37 +3277,37 @@
         <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="15" t="n">
-        <v>91.90000000000001</v>
+      <c r="M34" s="10" t="n">
+        <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q34" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R34" s="11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R34" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="S34" s="11" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="T34" s="11" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="U34" s="11" t="n">
-        <v>6.6</v>
+      <c r="S34" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3268,9 +3319,11 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3284,7 +3337,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -3310,34 +3365,34 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>11.1</v>
+        <v>19</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>1.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>172.4</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="S35" s="11" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="T35" s="11" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="U35" s="11" t="n">
-        <v>10.1</v>
+      <c r="S35" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>32</v>
@@ -3351,7 +3406,9 @@
       <c r="Y35" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="n">
+        <v>33.6</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3366,11 +3423,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="15" t="n">
-        <v>1.3</v>
+      <c r="D36" s="8" t="n">
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>25.8</v>
@@ -3385,38 +3442,40 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="M36" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>70.7</v>
+        <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S36" s="11" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T36" s="11" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="U36" s="11" t="n">
-        <v>17.4</v>
+      <c r="R36" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3425,12 +3484,14 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>8.5</v>
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3445,73 +3506,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="9" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="16" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="F37" s="11" t="n">
+      <c r="E37" s="9" t="n">
+        <v>1929.5</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <v>126.9</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="3" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>81</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="16" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K37" s="9" t="n">
         <v>949.9</v>
       </c>
-      <c r="L37" s="16" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="M37" s="16" t="n">
-        <v>92</v>
+      <c r="L37" s="9" t="n">
+        <v>951.1</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.5</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.2</v>
+        <v>150.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q37" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="16" t="n">
-        <v>119</v>
+      <c r="R37" s="9" t="n">
+        <v>117.3</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1230.4</v>
+        <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V37" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="W37" s="16" t="n">
-        <v>129.9</v>
+        <v>124.7</v>
+      </c>
+      <c r="V37" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
-      <c r="Z37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="n">
+        <v>247.3</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3526,16 +3589,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="11" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E38" s="11" t="n">
+      <c r="D38" s="9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G38" s="11" t="n">
+      <c r="F38" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3545,41 +3608,41 @@
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="16" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M38" s="16" t="n">
-        <v>46.8</v>
+      <c r="L38" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>17.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0.2</v>
+        <v>18.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>30.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q38" s="11" t="n">
+      <c r="Q38" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="S38" s="11" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="T38" s="11" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="U38" s="11" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V38" s="16" t="n">
-        <v>22.2</v>
+      <c r="S38" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V38" s="9" t="n">
+        <v>82.2</v>
       </c>
       <c r="W38" s="11" t="n">
         <v>25.2</v>
@@ -3588,9 +3651,11 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3606,38 +3671,38 @@
       </c>
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>18.5</v>
+        <v>32.6</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>8.5</v>
+        <v>25.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="12" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>796</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3645,29 +3710,33 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="15" t="n">
-        <v>42.6</v>
+      <c r="R39" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.1</v>
+        <v>22.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>69.2</v>
+        <v>61.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>27.8</v>
+        <v>21.9</v>
       </c>
       <c r="V39" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W39" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z39" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W39" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr"/>
-      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3681,7 +3750,9 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D40" s="11" t="n">
         <v>32.5</v>
       </c>
@@ -3695,25 +3766,25 @@
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>13.8</v>
+      <c r="M40" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>11.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3721,34 +3792,36 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R40" s="15" t="n">
-        <v>82.2</v>
+      <c r="Q40" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19.2</v>
+        <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y40" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V40" s="11" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="W40" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X40" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y40" s="11" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="Z40" s="11" t="n">
+        <v>826.2</v>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3763,43 +3836,45 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F41" s="3" t="n">
+      <c r="D41" s="11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F41" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.9</v>
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q41" s="3" t="n">
-        <v>2.4</v>
+        <v>29.4</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3808,24 +3883,26 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>2.4</v>
+        <v>37.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V41" s="15" t="n">
-        <v>2.4</v>
+        <v>9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>68.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3840,60 +3917,64 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="13" t="inlineStr"/>
+      <c r="E42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="15" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.3</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>8.6</v>
+      <c r="J42" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="15" t="n">
-        <v>98.40000000000001</v>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>13.3</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="R42" s="15" t="n">
+      <c r="Q42" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R42" s="10" t="n">
         <v>82</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>21.4</v>
+        <v>11.6</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V42" s="13" t="inlineStr"/>
-      <c r="W42" s="13" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="V42" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W42" s="10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -3926,7 +4007,7 @@
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="Q43" s="13" t="inlineStr"/>
       <c r="R43" s="13" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -3965,7 +4046,7 @@
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
       <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -3988,72 +4069,76 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="16" t="n">
+      <c r="C45" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="F45" s="16" t="n">
-        <v>162</v>
+      <c r="F45" s="9" t="n">
+        <v>102</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>5.4</v>
+        <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>62.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K45" s="16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L45" s="16" t="n">
-        <v>141.1</v>
-      </c>
-      <c r="M45" s="16" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>8.9</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>2366.2</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="14" t="inlineStr"/>
-      <c r="R45" s="16" t="n">
-        <v>91.59999999999999</v>
+      <c r="Q45" s="9" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="R45" s="9" t="n">
+        <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>32.7</v>
+        <v>132.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="V45" s="16" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="W45" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V45" s="9" t="n">
+        <v>892.7</v>
+      </c>
+      <c r="W45" s="9" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>221.2</v>
+        <v>19327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4068,69 +4153,75 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E46" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="E46" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="G46" s="11" t="n">
-        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>30.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="16" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="M46" s="16" t="n">
-        <v>11.9</v>
+        <v>0.4</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q46" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="16" t="n">
+      <c r="R46" s="9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W46" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V46" s="16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W46" s="16" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>82.3</v>
-      </c>
       <c r="Y46" s="3" t="n">
-        <v>87208.5</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+        <v>60.2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
